--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133882634</v>
+        <v>133884534</v>
       </c>
       <c r="B2" t="n">
         <v>57958</v>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472920</v>
+        <v>473064</v>
       </c>
       <c r="R2" t="n">
-        <v>7024099</v>
+        <v>7023842</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133881460</v>
+        <v>133882634</v>
       </c>
       <c r="B3" t="n">
         <v>57958</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473072</v>
+        <v>472920</v>
       </c>
       <c r="R3" t="n">
-        <v>7023730</v>
+        <v>7024099</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133884534</v>
+        <v>133881460</v>
       </c>
       <c r="B4" t="n">
         <v>57958</v>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473064</v>
+        <v>473072</v>
       </c>
       <c r="R4" t="n">
-        <v>7023842</v>
+        <v>7023730</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,48 +1026,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133880452</v>
+        <v>133883011</v>
       </c>
       <c r="B5" t="n">
-        <v>91922</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472967</v>
+        <v>472886</v>
       </c>
       <c r="R5" t="n">
-        <v>7023552</v>
+        <v>7024237</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,48 +1133,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883011</v>
+        <v>133880452</v>
       </c>
       <c r="B6" t="n">
-        <v>80467</v>
+        <v>91926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472886</v>
+        <v>472967</v>
       </c>
       <c r="R6" t="n">
-        <v>7024237</v>
+        <v>7023552</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1243,7 @@
         <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>99134</v>
+        <v>99138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R9" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B10" t="n">
         <v>57958</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R10" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1700,7 +1700,7 @@
         <v>133880223</v>
       </c>
       <c r="B11" t="n">
-        <v>92382</v>
+        <v>92386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>133883311</v>
       </c>
       <c r="B14" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>133881639</v>
       </c>
       <c r="B17" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133880347</v>
+        <v>133881340</v>
       </c>
       <c r="B19" t="n">
-        <v>91922</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,37 +2618,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472980</v>
+        <v>473047</v>
       </c>
       <c r="R19" t="n">
-        <v>7023567</v>
+        <v>7023739</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2677,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2687,12 +2692,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881340</v>
+        <v>133880347</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>91926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,42 +2852,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473047</v>
+        <v>472980</v>
       </c>
       <c r="R21" t="n">
-        <v>7023739</v>
+        <v>7023567</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880344</v>
+        <v>133883056</v>
       </c>
       <c r="B23" t="n">
-        <v>92221</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,37 +3081,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472980</v>
+        <v>472863</v>
       </c>
       <c r="R23" t="n">
-        <v>7023567</v>
+        <v>7024224</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>92225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R24" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3257,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,12 +3266,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883056</v>
+        <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,46 +3309,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472863</v>
+        <v>472977</v>
       </c>
       <c r="R25" t="n">
-        <v>7024224</v>
+        <v>7023797</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3535,7 +3535,7 @@
         <v>133882394</v>
       </c>
       <c r="B27" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>133884576</v>
       </c>
       <c r="B28" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1026,48 +1026,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883011</v>
+        <v>133880452</v>
       </c>
       <c r="B5" t="n">
-        <v>80467</v>
+        <v>91928</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472886</v>
+        <v>472967</v>
       </c>
       <c r="R5" t="n">
-        <v>7024237</v>
+        <v>7023552</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,48 +1133,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133880452</v>
+        <v>133883011</v>
       </c>
       <c r="B6" t="n">
-        <v>91926</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472967</v>
+        <v>472886</v>
       </c>
       <c r="R6" t="n">
-        <v>7023552</v>
+        <v>7024237</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1243,7 @@
         <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R9" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1580,53 +1580,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133882938</v>
+        <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472887</v>
+        <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7024233</v>
+        <v>7023561</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,48 +1692,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133880223</v>
+        <v>133883162</v>
       </c>
       <c r="B11" t="n">
-        <v>92386</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R11" t="n">
-        <v>7023561</v>
+        <v>7024244</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2046,7 +2046,7 @@
         <v>133883311</v>
       </c>
       <c r="B14" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133881311</v>
+        <v>133883623</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,42 +2161,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473049</v>
+        <v>473057</v>
       </c>
       <c r="R15" t="n">
-        <v>7023744</v>
+        <v>7024202</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2225,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,12 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883623</v>
+        <v>133881311</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,46 +2277,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473057</v>
+        <v>473049</v>
       </c>
       <c r="R16" t="n">
-        <v>7024202</v>
+        <v>7023744</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2346,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2351,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,7 +2386,7 @@
         <v>133881639</v>
       </c>
       <c r="B17" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133881340</v>
+        <v>133880347</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,42 +2618,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473047</v>
+        <v>472980</v>
       </c>
       <c r="R19" t="n">
-        <v>7023739</v>
+        <v>7023567</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2677,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,12 +2687,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,7 +2719,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133881616</v>
+        <v>133881340</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2755,7 +2750,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2764,13 +2759,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473083</v>
+        <v>473047</v>
       </c>
       <c r="R20" t="n">
-        <v>7023715</v>
+        <v>7023739</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,12 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133880347</v>
+        <v>133881616</v>
       </c>
       <c r="B21" t="n">
-        <v>91926</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,37 +2847,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472980</v>
+        <v>473083</v>
       </c>
       <c r="R21" t="n">
-        <v>7023567</v>
+        <v>7023715</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på bra</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883056</v>
+        <v>133880344</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,46 +3081,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472863</v>
+        <v>472980</v>
       </c>
       <c r="R23" t="n">
-        <v>7024224</v>
+        <v>7023567</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880344</v>
+        <v>133883056</v>
       </c>
       <c r="B24" t="n">
-        <v>92225</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,37 +3193,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472980</v>
+        <v>472863</v>
       </c>
       <c r="R24" t="n">
-        <v>7023567</v>
+        <v>7024224</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,12 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3535,7 +3535,7 @@
         <v>133882394</v>
       </c>
       <c r="B27" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>133884576</v>
       </c>
       <c r="B28" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,48 +1240,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R7" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,57 +1356,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R8" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,57 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R7" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,48 +1347,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R8" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,53 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882938</v>
+        <v>133880223</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472887</v>
+        <v>472980</v>
       </c>
       <c r="R9" t="n">
-        <v>7024233</v>
+        <v>7023561</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,48 +1575,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880223</v>
+        <v>133883162</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R10" t="n">
-        <v>7023561</v>
+        <v>7024244</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B11" t="n">
         <v>57958</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R11" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880344</v>
+        <v>133880910</v>
       </c>
       <c r="B23" t="n">
-        <v>92227</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,34 +3081,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472980</v>
+        <v>472977</v>
       </c>
       <c r="R23" t="n">
-        <v>7023567</v>
+        <v>7023797</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3140,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3155,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883056</v>
+        <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,46 +3198,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472863</v>
+        <v>472980</v>
       </c>
       <c r="R24" t="n">
-        <v>7024224</v>
+        <v>7023567</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3267,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880910</v>
+        <v>133883056</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,42 +3310,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472977</v>
+        <v>472863</v>
       </c>
       <c r="R25" t="n">
-        <v>7023797</v>
+        <v>7024224</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,48 +1240,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R7" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,57 +1356,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R8" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,48 +1463,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133880223</v>
+        <v>133882938</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472980</v>
+        <v>472887</v>
       </c>
       <c r="R9" t="n">
-        <v>7023561</v>
+        <v>7024233</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1548,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1580,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883162</v>
+        <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472936</v>
+        <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7024244</v>
+        <v>7023561</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B11" t="n">
         <v>57958</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R11" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,42 +1820,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,37 +2044,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>472957</v>
       </c>
       <c r="R14" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2118,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>92227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,39 +3081,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R23" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3145,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,12 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880344</v>
+        <v>133883056</v>
       </c>
       <c r="B24" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,37 +3193,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472980</v>
+        <v>472863</v>
       </c>
       <c r="R24" t="n">
-        <v>7023567</v>
+        <v>7024224</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,12 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883056</v>
+        <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,46 +3309,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472863</v>
+        <v>472977</v>
       </c>
       <c r="R25" t="n">
-        <v>7024224</v>
+        <v>7023797</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,57 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R7" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,48 +1347,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R8" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,53 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882938</v>
+        <v>133880223</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472887</v>
+        <v>472980</v>
       </c>
       <c r="R9" t="n">
-        <v>7024233</v>
+        <v>7023561</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,48 +1575,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880223</v>
+        <v>133883162</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R10" t="n">
-        <v>7023561</v>
+        <v>7024244</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B11" t="n">
         <v>57958</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R11" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B12" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,37 +1820,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,42 +2054,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>472957</v>
       </c>
       <c r="R14" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1463,48 +1463,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133880223</v>
+        <v>133882938</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472980</v>
+        <v>472887</v>
       </c>
       <c r="R9" t="n">
-        <v>7023561</v>
+        <v>7024233</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1548,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1580,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883162</v>
+        <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472936</v>
+        <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7024244</v>
+        <v>7023561</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B11" t="n">
         <v>57958</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R11" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,42 +1820,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,37 +2044,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>472957</v>
       </c>
       <c r="R14" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2118,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133884534</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>133882634</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>133881460</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,48 +1026,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133880452</v>
+        <v>133883011</v>
       </c>
       <c r="B5" t="n">
-        <v>91928</v>
+        <v>80481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472967</v>
+        <v>472886</v>
       </c>
       <c r="R5" t="n">
-        <v>7023552</v>
+        <v>7024237</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,48 +1133,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883011</v>
+        <v>133880452</v>
       </c>
       <c r="B6" t="n">
-        <v>80467</v>
+        <v>91947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472886</v>
+        <v>472967</v>
       </c>
       <c r="R6" t="n">
-        <v>7024237</v>
+        <v>7023552</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,48 +1240,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R7" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,57 +1356,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R8" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R9" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1583,7 +1583,7 @@
         <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>92379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R11" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1812,7 +1812,7 @@
         <v>133883311</v>
       </c>
       <c r="B12" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133881577</v>
+        <v>133880505</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,22 +1947,22 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473086</v>
+        <v>472957</v>
       </c>
       <c r="R13" t="n">
-        <v>7023722</v>
+        <v>7023584</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133880505</v>
+        <v>133881577</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,22 +2064,22 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472957</v>
+        <v>473086</v>
       </c>
       <c r="R14" t="n">
-        <v>7023584</v>
+        <v>7023722</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2153,7 +2153,7 @@
         <v>133883623</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>133881311</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133881639</v>
+        <v>133882856</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,37 +2394,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473084</v>
+        <v>472936</v>
       </c>
       <c r="R17" t="n">
-        <v>7023717</v>
+        <v>7024232</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2468,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre och färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133882856</v>
+        <v>133881639</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,42 +2511,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472936</v>
+        <v>473084</v>
       </c>
       <c r="R18" t="n">
-        <v>7024232</v>
+        <v>7023717</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,12 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133880347</v>
+        <v>133881340</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,37 +2618,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472980</v>
+        <v>473047</v>
       </c>
       <c r="R19" t="n">
-        <v>7023567</v>
+        <v>7023739</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2677,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2687,12 +2692,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133881340</v>
+        <v>133880347</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,42 +2735,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473047</v>
+        <v>472980</v>
       </c>
       <c r="R20" t="n">
-        <v>7023739</v>
+        <v>7023567</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,7 +2839,7 @@
         <v>133881616</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>133884248</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>133880344</v>
       </c>
       <c r="B23" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883056</v>
+        <v>133880910</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,46 +3193,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472863</v>
+        <v>472977</v>
       </c>
       <c r="R24" t="n">
-        <v>7024224</v>
+        <v>7023797</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3267,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880910</v>
+        <v>133883056</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,42 +3310,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472977</v>
+        <v>472863</v>
       </c>
       <c r="R25" t="n">
-        <v>7023797</v>
+        <v>7024224</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,7 +3418,7 @@
         <v>133883043</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>133882394</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>133884576</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,57 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>99168</v>
+        <v>91947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R7" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,48 +1347,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>91947</v>
+        <v>99168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R8" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880344</v>
+        <v>133883056</v>
       </c>
       <c r="B23" t="n">
-        <v>92218</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,37 +3081,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472980</v>
+        <v>472863</v>
       </c>
       <c r="R23" t="n">
-        <v>7023567</v>
+        <v>7024224</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>57965</v>
+        <v>92218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R24" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3257,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,12 +3266,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883056</v>
+        <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,46 +3309,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472863</v>
+        <v>472977</v>
       </c>
       <c r="R25" t="n">
-        <v>7024224</v>
+        <v>7023797</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133884534</v>
+        <v>133882634</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473064</v>
+        <v>472920</v>
       </c>
       <c r="R2" t="n">
-        <v>7023842</v>
+        <v>7024099</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133882634</v>
+        <v>133884534</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472920</v>
+        <v>473064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024099</v>
+        <v>7023842</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,7 +912,7 @@
         <v>133881460</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>133883011</v>
       </c>
       <c r="B5" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>133880452</v>
       </c>
       <c r="B6" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R9" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1583,7 +1583,7 @@
         <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>92379</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R11" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B12" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,37 +1820,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B13" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,42 +1937,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>472957</v>
       </c>
       <c r="R13" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,12 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,7 +2036,7 @@
         <v>133881577</v>
       </c>
       <c r="B14" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883623</v>
+        <v>133881311</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,46 +2161,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473057</v>
+        <v>473049</v>
       </c>
       <c r="R15" t="n">
-        <v>7024202</v>
+        <v>7023744</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2235,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133881311</v>
+        <v>133883623</v>
       </c>
       <c r="B16" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,42 +2278,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473049</v>
+        <v>473057</v>
       </c>
       <c r="R16" t="n">
-        <v>7023744</v>
+        <v>7024202</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,12 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133882856</v>
+        <v>133881639</v>
       </c>
       <c r="B17" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,42 +2394,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472936</v>
+        <v>473084</v>
       </c>
       <c r="R17" t="n">
-        <v>7024232</v>
+        <v>7023717</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,12 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133881639</v>
+        <v>133882856</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,37 +2501,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473084</v>
+        <v>472936</v>
       </c>
       <c r="R18" t="n">
-        <v>7023717</v>
+        <v>7024232</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2575,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre och färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133881340</v>
+        <v>133880347</v>
       </c>
       <c r="B19" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,42 +2618,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473047</v>
+        <v>472980</v>
       </c>
       <c r="R19" t="n">
-        <v>7023739</v>
+        <v>7023567</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2677,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,12 +2687,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2719,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133880347</v>
+        <v>133881616</v>
       </c>
       <c r="B20" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,37 +2730,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472980</v>
+        <v>473083</v>
       </c>
       <c r="R20" t="n">
-        <v>7023567</v>
+        <v>7023715</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på bra</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881616</v>
+        <v>133881340</v>
       </c>
       <c r="B21" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473083</v>
+        <v>473047</v>
       </c>
       <c r="R21" t="n">
-        <v>7023715</v>
+        <v>7023739</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,7 +2956,7 @@
         <v>133884248</v>
       </c>
       <c r="B22" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>133883056</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>133883043</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>133882394</v>
       </c>
       <c r="B27" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>133884576</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133882634</v>
+        <v>133881460</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472920</v>
+        <v>473072</v>
       </c>
       <c r="R2" t="n">
-        <v>7024099</v>
+        <v>7023730</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133881460</v>
+        <v>133882634</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473072</v>
+        <v>472920</v>
       </c>
       <c r="R4" t="n">
-        <v>7023730</v>
+        <v>7024099</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1240,48 +1240,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R7" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,57 +1356,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B8" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R8" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,53 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882938</v>
+        <v>133880223</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472887</v>
+        <v>472980</v>
       </c>
       <c r="R9" t="n">
-        <v>7024233</v>
+        <v>7023561</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,48 +1575,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880223</v>
+        <v>133883162</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R10" t="n">
-        <v>7023561</v>
+        <v>7024244</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883162</v>
+        <v>133882938</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472936</v>
+        <v>472887</v>
       </c>
       <c r="R11" t="n">
-        <v>7024244</v>
+        <v>7024233</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,42 +1820,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,37 +1927,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>472957</v>
       </c>
       <c r="R13" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2001,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2383,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133881639</v>
+        <v>133882856</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,37 +2394,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473084</v>
+        <v>472936</v>
       </c>
       <c r="R17" t="n">
-        <v>7023717</v>
+        <v>7024232</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2468,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre och färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133882856</v>
+        <v>133881639</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,42 +2511,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472936</v>
+        <v>473084</v>
       </c>
       <c r="R18" t="n">
-        <v>7024232</v>
+        <v>7023717</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,12 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133880347</v>
+        <v>133881340</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,37 +2618,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472980</v>
+        <v>473047</v>
       </c>
       <c r="R19" t="n">
-        <v>7023567</v>
+        <v>7023739</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2677,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2687,12 +2692,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133881616</v>
+        <v>133880347</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,42 +2735,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473083</v>
+        <v>472980</v>
       </c>
       <c r="R20" t="n">
-        <v>7023715</v>
+        <v>7023567</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,7 +2836,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881340</v>
+        <v>133881616</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2867,7 +2867,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473047</v>
+        <v>473083</v>
       </c>
       <c r="R21" t="n">
-        <v>7023739</v>
+        <v>7023715</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på bra</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883056</v>
+        <v>133880344</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>92228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,46 +3081,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472863</v>
+        <v>472980</v>
       </c>
       <c r="R23" t="n">
-        <v>7024224</v>
+        <v>7023567</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880344</v>
+        <v>133880910</v>
       </c>
       <c r="B24" t="n">
-        <v>92228</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,34 +3193,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472980</v>
+        <v>472977</v>
       </c>
       <c r="R24" t="n">
-        <v>7023567</v>
+        <v>7023797</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3256,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,12 +3267,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880910</v>
+        <v>133883056</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,42 +3310,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472977</v>
+        <v>472863</v>
       </c>
       <c r="R25" t="n">
-        <v>7023797</v>
+        <v>7024224</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133881460</v>
+        <v>133884534</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473072</v>
+        <v>473064</v>
       </c>
       <c r="R2" t="n">
-        <v>7023730</v>
+        <v>7023842</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133884534</v>
+        <v>133882634</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473064</v>
+        <v>472920</v>
       </c>
       <c r="R3" t="n">
-        <v>7023842</v>
+        <v>7024099</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133882634</v>
+        <v>133881460</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472920</v>
+        <v>473072</v>
       </c>
       <c r="R4" t="n">
-        <v>7024099</v>
+        <v>7023730</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1463,48 +1463,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133880223</v>
+        <v>133883162</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R9" t="n">
-        <v>7023561</v>
+        <v>7024244</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1548,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1580,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883162</v>
+        <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472936</v>
+        <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7024244</v>
+        <v>7023561</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133881311</v>
+        <v>133883623</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,42 +2161,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473049</v>
+        <v>473057</v>
       </c>
       <c r="R15" t="n">
-        <v>7023744</v>
+        <v>7024202</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2225,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,12 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883623</v>
+        <v>133881311</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,46 +2277,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473057</v>
+        <v>473049</v>
       </c>
       <c r="R16" t="n">
-        <v>7024202</v>
+        <v>7023744</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2346,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2351,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880344</v>
+        <v>133883056</v>
       </c>
       <c r="B23" t="n">
-        <v>92228</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,37 +3081,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472980</v>
+        <v>472863</v>
       </c>
       <c r="R23" t="n">
-        <v>7023567</v>
+        <v>7024224</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>92228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R24" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3257,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,12 +3266,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883056</v>
+        <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,46 +3309,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472863</v>
+        <v>472977</v>
       </c>
       <c r="R25" t="n">
-        <v>7024224</v>
+        <v>7023797</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133884534</v>
+        <v>133882634</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473064</v>
+        <v>472920</v>
       </c>
       <c r="R2" t="n">
-        <v>7023842</v>
+        <v>7024099</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133882634</v>
+        <v>133884534</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472920</v>
+        <v>473064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024099</v>
+        <v>7023842</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1029,7 +1029,7 @@
         <v>133883011</v>
       </c>
       <c r="B5" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>133880452</v>
       </c>
       <c r="B6" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>133880251</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>133880108</v>
       </c>
       <c r="B8" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,53 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883162</v>
+        <v>133880223</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>92391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472936</v>
+        <v>472980</v>
       </c>
       <c r="R9" t="n">
-        <v>7024244</v>
+        <v>7023561</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,48 +1575,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880223</v>
+        <v>133882938</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472980</v>
+        <v>472887</v>
       </c>
       <c r="R10" t="n">
-        <v>7023561</v>
+        <v>7024233</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133882938</v>
+        <v>133883162</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472887</v>
+        <v>472936</v>
       </c>
       <c r="R11" t="n">
-        <v>7024233</v>
+        <v>7024244</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1812,7 +1812,7 @@
         <v>133883311</v>
       </c>
       <c r="B12" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>133883623</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>133881639</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>133880347</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>133883056</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880344</v>
+        <v>133880910</v>
       </c>
       <c r="B24" t="n">
-        <v>92228</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,34 +3197,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472980</v>
+        <v>472977</v>
       </c>
       <c r="R24" t="n">
-        <v>7023567</v>
+        <v>7023797</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3256,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,12 +3271,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>92230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,39 +3314,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R25" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133882394</v>
+        <v>133884576</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472916</v>
+        <v>473076</v>
       </c>
       <c r="R27" t="n">
-        <v>7023822</v>
+        <v>7023856</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3612,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133884576</v>
+        <v>133882394</v>
       </c>
       <c r="B28" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3674,13 +3679,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473076</v>
+        <v>472916</v>
       </c>
       <c r="R28" t="n">
-        <v>7023856</v>
+        <v>7023822</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3709,7 +3714,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,12 +3724,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -1240,57 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880251</v>
+        <v>133880108</v>
       </c>
       <c r="B7" t="n">
-        <v>99180</v>
+        <v>91959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472980</v>
+        <v>472970</v>
       </c>
       <c r="R7" t="n">
-        <v>7023561</v>
+        <v>7023509</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,48 +1347,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880108</v>
+        <v>133880251</v>
       </c>
       <c r="B8" t="n">
-        <v>91959</v>
+        <v>99180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472970</v>
+        <v>472980</v>
       </c>
       <c r="R8" t="n">
-        <v>7023509</v>
+        <v>7023561</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,48 +1463,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133880223</v>
+        <v>133882938</v>
       </c>
       <c r="B9" t="n">
-        <v>92391</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472980</v>
+        <v>472887</v>
       </c>
       <c r="R9" t="n">
-        <v>7023561</v>
+        <v>7024233</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1548,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1580,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133882938</v>
+        <v>133880223</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>92391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472887</v>
+        <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7024233</v>
+        <v>7023561</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883311</v>
+        <v>133880505</v>
       </c>
       <c r="B12" t="n">
-        <v>91959</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,37 +1820,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>472957</v>
       </c>
       <c r="R12" t="n">
-        <v>7024221</v>
+        <v>7023584</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133880505</v>
+        <v>133883311</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>91959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,42 +1937,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>472957</v>
       </c>
       <c r="R13" t="n">
-        <v>7023584</v>
+        <v>7024221</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,12 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883623</v>
+        <v>133881311</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,46 +2161,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473057</v>
+        <v>473049</v>
       </c>
       <c r="R15" t="n">
-        <v>7024202</v>
+        <v>7023744</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2235,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133881311</v>
+        <v>133883623</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,42 +2278,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473049</v>
+        <v>473057</v>
       </c>
       <c r="R16" t="n">
-        <v>7023744</v>
+        <v>7024202</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,12 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133882856</v>
+        <v>133881639</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>91959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,42 +2394,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472936</v>
+        <v>473084</v>
       </c>
       <c r="R17" t="n">
-        <v>7024232</v>
+        <v>7023717</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,12 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133881639</v>
+        <v>133882856</v>
       </c>
       <c r="B18" t="n">
-        <v>91959</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,37 +2501,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473084</v>
+        <v>472936</v>
       </c>
       <c r="R18" t="n">
-        <v>7023717</v>
+        <v>7024232</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2575,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre och färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133881340</v>
+        <v>133880347</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>91959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,42 +2618,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473047</v>
+        <v>472980</v>
       </c>
       <c r="R19" t="n">
-        <v>7023739</v>
+        <v>7023567</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2677,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,12 +2687,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2719,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133880347</v>
+        <v>133881616</v>
       </c>
       <c r="B20" t="n">
-        <v>91959</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,37 +2730,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472980</v>
+        <v>473083</v>
       </c>
       <c r="R20" t="n">
-        <v>7023567</v>
+        <v>7023715</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på bra</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,7 +2836,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881616</v>
+        <v>133881340</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2867,7 +2867,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473083</v>
+        <v>473047</v>
       </c>
       <c r="R21" t="n">
-        <v>7023715</v>
+        <v>7023739</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880910</v>
+        <v>133880344</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>92230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472977</v>
+        <v>472980</v>
       </c>
       <c r="R24" t="n">
-        <v>7023797</v>
+        <v>7023567</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3261,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,12 +3266,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880344</v>
+        <v>133880910</v>
       </c>
       <c r="B25" t="n">
-        <v>92230</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,34 +3309,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472980</v>
+        <v>472977</v>
       </c>
       <c r="R25" t="n">
-        <v>7023567</v>
+        <v>7023797</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133884576</v>
+        <v>133882394</v>
       </c>
       <c r="B27" t="n">
         <v>91959</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473076</v>
+        <v>472916</v>
       </c>
       <c r="R27" t="n">
-        <v>7023856</v>
+        <v>7023822</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,12 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,7 +3639,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133882394</v>
+        <v>133884576</v>
       </c>
       <c r="B28" t="n">
         <v>91959</v>
@@ -3679,13 +3674,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472916</v>
+        <v>473076</v>
       </c>
       <c r="R28" t="n">
-        <v>7023822</v>
+        <v>7023856</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3724,7 +3719,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133884534</v>
+        <v>133883011</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>80478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473064</v>
+        <v>472886</v>
       </c>
       <c r="R2" t="n">
-        <v>7023842</v>
+        <v>7024237</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133882634</v>
+        <v>133880452</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472920</v>
+        <v>472967</v>
       </c>
       <c r="R3" t="n">
-        <v>7024099</v>
+        <v>7023552</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +889,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133881460</v>
+        <v>133880251</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473072</v>
+        <v>472980</v>
       </c>
       <c r="R4" t="n">
-        <v>7023730</v>
+        <v>7023561</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,48 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883011</v>
+        <v>133880108</v>
       </c>
       <c r="B5" t="n">
-        <v>80478</v>
+        <v>91960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472886</v>
+        <v>472970</v>
       </c>
       <c r="R5" t="n">
-        <v>7024237</v>
+        <v>7023509</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,32 +1112,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133880452</v>
+        <v>133880223</v>
       </c>
       <c r="B6" t="n">
-        <v>91960</v>
+        <v>92392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472967</v>
+        <v>472980</v>
       </c>
       <c r="R6" t="n">
-        <v>7023552</v>
+        <v>7023561</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1192,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,57 +1224,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880251</v>
+        <v>133883311</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472980</v>
+        <v>472957</v>
       </c>
       <c r="R7" t="n">
-        <v>7023561</v>
+        <v>7024221</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133880108</v>
+        <v>133883623</v>
       </c>
       <c r="B8" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,37 +1342,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472970</v>
+        <v>473057</v>
       </c>
       <c r="R8" t="n">
-        <v>7023509</v>
+        <v>7024202</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883162</v>
+        <v>133881639</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,39 +1458,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472936</v>
+        <v>473084</v>
       </c>
       <c r="R9" t="n">
-        <v>7024244</v>
+        <v>7023717</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1538,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,32 +1554,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880223</v>
+        <v>133880347</v>
       </c>
       <c r="B10" t="n">
-        <v>92392</v>
+        <v>91960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1592,10 @@
         <v>472980</v>
       </c>
       <c r="R10" t="n">
-        <v>7023561</v>
+        <v>7023567</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1634,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133882938</v>
+        <v>133883056</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,42 +1677,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472887</v>
+        <v>472863</v>
       </c>
       <c r="R11" t="n">
-        <v>7024233</v>
+        <v>7024224</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883311</v>
+        <v>133880344</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>92231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,37 +1793,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472957</v>
+        <v>472980</v>
       </c>
       <c r="R12" t="n">
-        <v>7024221</v>
+        <v>7023567</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1862,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133880505</v>
+        <v>133882394</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,42 +1905,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472957</v>
+        <v>472916</v>
       </c>
       <c r="R13" t="n">
-        <v>7023584</v>
+        <v>7023822</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,12 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133881577</v>
+        <v>133884576</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,39 +2012,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473086</v>
+        <v>473076</v>
       </c>
       <c r="R14" t="n">
-        <v>7023722</v>
+        <v>7023856</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2108,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883623</v>
+        <v>133881460</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,46 +2124,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473057</v>
+        <v>473072</v>
       </c>
       <c r="R15" t="n">
-        <v>7024202</v>
+        <v>7023730</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2198,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,7 +2230,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133881311</v>
+        <v>133884534</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2297,7 +2261,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2306,13 +2270,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473049</v>
+        <v>473064</v>
       </c>
       <c r="R16" t="n">
-        <v>7023744</v>
+        <v>7023842</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2383,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133882856</v>
+        <v>133882634</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2419,17 +2383,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472936</v>
+        <v>472920</v>
       </c>
       <c r="R17" t="n">
-        <v>7024232</v>
+        <v>7024099</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,12 +2432,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133881639</v>
+        <v>133883162</v>
       </c>
       <c r="B18" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,34 +2475,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473084</v>
+        <v>472936</v>
       </c>
       <c r="R18" t="n">
-        <v>7023717</v>
+        <v>7024244</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2570,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2549,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,7 +2581,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133881340</v>
+        <v>133882938</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2638,22 +2612,22 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473047</v>
+        <v>472887</v>
       </c>
       <c r="R19" t="n">
-        <v>7023739</v>
+        <v>7024233</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2724,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133880347</v>
+        <v>133882856</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,37 +2709,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472980</v>
+        <v>472936</v>
       </c>
       <c r="R20" t="n">
-        <v>7023567</v>
+        <v>7024232</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2804,12 +2783,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Ringhack på gran, äldre och färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,7 +2815,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881616</v>
+        <v>133881340</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2867,7 +2846,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2876,13 +2855,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473083</v>
+        <v>473047</v>
       </c>
       <c r="R21" t="n">
-        <v>7023715</v>
+        <v>7023739</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2900,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,7 +2932,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133884248</v>
+        <v>133883043</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2989,14 +2968,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472989</v>
+        <v>472887</v>
       </c>
       <c r="R22" t="n">
-        <v>7024136</v>
+        <v>7024224</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3028,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3038,12 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack och födosöksspår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883056</v>
+        <v>133880505</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,46 +3060,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472863</v>
+        <v>472957</v>
       </c>
       <c r="R23" t="n">
-        <v>7024224</v>
+        <v>7023584</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3124,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3134,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3166,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133880344</v>
+        <v>133881577</v>
       </c>
       <c r="B24" t="n">
-        <v>92231</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,37 +3177,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472980</v>
+        <v>473086</v>
       </c>
       <c r="R24" t="n">
-        <v>7023567</v>
+        <v>7023722</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,7 +3241,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,12 +3251,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,7 +3283,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133880910</v>
+        <v>133881311</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -3338,13 +3323,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472977</v>
+        <v>473049</v>
       </c>
       <c r="R25" t="n">
-        <v>7023797</v>
+        <v>7023744</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,12 +3368,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,7 +3400,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883043</v>
+        <v>133881616</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3446,22 +3431,22 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472887</v>
+        <v>473083</v>
       </c>
       <c r="R26" t="n">
-        <v>7024224</v>
+        <v>7023715</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3490,7 +3475,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,12 +3485,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack och födosöksspår på gran</t>
+          <t>Ringhack på bra</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,10 +3517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133882394</v>
+        <v>133884248</v>
       </c>
       <c r="B27" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3543,37 +3528,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472916</v>
+        <v>472989</v>
       </c>
       <c r="R27" t="n">
-        <v>7023822</v>
+        <v>7024136</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3602,7 +3592,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3602,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133884576</v>
+        <v>133880910</v>
       </c>
       <c r="B28" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,37 +3645,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473076</v>
+        <v>472977</v>
       </c>
       <c r="R28" t="n">
-        <v>7023856</v>
+        <v>7023797</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133883011</v>
+        <v>133880452</v>
       </c>
       <c r="B2" t="n">
-        <v>80478</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472886</v>
+        <v>472967</v>
       </c>
       <c r="R2" t="n">
-        <v>7024237</v>
+        <v>7023552</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133880452</v>
+        <v>133883011</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>80485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472967</v>
+        <v>472886</v>
       </c>
       <c r="R3" t="n">
-        <v>7023552</v>
+        <v>7024237</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>133880251</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>133880108</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>133880223</v>
       </c>
       <c r="B6" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>133883311</v>
       </c>
       <c r="B7" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>133883623</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>133881639</v>
       </c>
       <c r="B9" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>133880347</v>
       </c>
       <c r="B10" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>133883056</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>133880344</v>
       </c>
       <c r="B12" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133882394</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>133884576</v>
       </c>
       <c r="B14" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133881460</v>
+        <v>133884534</v>
       </c>
       <c r="B15" t="n">
         <v>57975</v>
@@ -2144,7 +2144,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473072</v>
+        <v>473064</v>
       </c>
       <c r="R15" t="n">
-        <v>7023730</v>
+        <v>7023842</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,7 +2230,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133884534</v>
+        <v>133882634</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2261,7 +2261,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473064</v>
+        <v>472920</v>
       </c>
       <c r="R16" t="n">
-        <v>7023842</v>
+        <v>7024099</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2347,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133882634</v>
+        <v>133881460</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472920</v>
+        <v>473072</v>
       </c>
       <c r="R17" t="n">
-        <v>7024099</v>
+        <v>7023730</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 20739-2026 artfynd.xlsx
+++ b/artfynd/A 20739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133880452</v>
+        <v>133880344</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472967</v>
+        <v>472980</v>
       </c>
       <c r="R2" t="n">
-        <v>7023552</v>
+        <v>7023567</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883011</v>
+        <v>133880108</v>
       </c>
       <c r="B3" t="n">
-        <v>80485</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472886</v>
+        <v>472970</v>
       </c>
       <c r="R3" t="n">
-        <v>7024237</v>
+        <v>7023509</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,44 +894,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133880251</v>
+        <v>133880347</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
@@ -936,10 +932,10 @@
         <v>472980</v>
       </c>
       <c r="R4" t="n">
-        <v>7023561</v>
+        <v>7023567</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133880108</v>
+        <v>133880452</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472970</v>
+        <v>472967</v>
       </c>
       <c r="R5" t="n">
-        <v>7023509</v>
+        <v>7023552</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,48 +1113,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133880223</v>
+        <v>133881293</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472980</v>
+        <v>473036</v>
       </c>
       <c r="R6" t="n">
-        <v>7023561</v>
+        <v>7023744</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,12 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på gammal granlåga</t>
+          <t>På gamma granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883311</v>
+        <v>133881639</v>
       </c>
       <c r="B7" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,17 +1256,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472957</v>
+        <v>473084</v>
       </c>
       <c r="R7" t="n">
-        <v>7024221</v>
+        <v>7023717</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883623</v>
+        <v>133882394</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,46 +1343,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473057</v>
+        <v>472916</v>
       </c>
       <c r="R8" t="n">
-        <v>7024202</v>
+        <v>7023822</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133881639</v>
+        <v>133883311</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,17 +1470,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473084</v>
+        <v>472957</v>
       </c>
       <c r="R9" t="n">
-        <v>7023717</v>
+        <v>7024221</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1517,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880347</v>
+        <v>133884576</v>
       </c>
       <c r="B10" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,17 +1577,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472980</v>
+        <v>473076</v>
       </c>
       <c r="R10" t="n">
-        <v>7023567</v>
+        <v>7023856</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1666,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883056</v>
+        <v>133880223</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>92406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,46 +1669,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472863</v>
+        <v>472980</v>
       </c>
       <c r="R11" t="n">
-        <v>7024224</v>
+        <v>7023561</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,48 +1770,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133880344</v>
+        <v>133880045</v>
       </c>
       <c r="B12" t="n">
-        <v>92238</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472980</v>
+        <v>472954</v>
       </c>
       <c r="R12" t="n">
-        <v>7023567</v>
+        <v>7023482</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,12 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal granlåga tsm med rynkskinn och ullticka</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,48 +1886,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133882394</v>
+        <v>133881870</v>
       </c>
       <c r="B13" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472916</v>
+        <v>473091</v>
       </c>
       <c r="R13" t="n">
-        <v>7023822</v>
+        <v>7023687</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1975,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,48 +2002,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133884576</v>
+        <v>133883056</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473076</v>
+        <v>472863</v>
       </c>
       <c r="R14" t="n">
-        <v>7023856</v>
+        <v>7024224</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2081,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2091,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,53 +2118,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133884534</v>
+        <v>133883623</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473064</v>
+        <v>473057</v>
       </c>
       <c r="R15" t="n">
-        <v>7023842</v>
+        <v>7024202</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,7 +2197,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,12 +2207,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,53 +2234,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133882634</v>
+        <v>133883011</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Lomtjärnen, Lomtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472920</v>
+        <v>472886</v>
       </c>
       <c r="R16" t="n">
-        <v>7024099</v>
+        <v>7024237</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,12 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,7 +2341,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133881460</v>
+        <v>133880505</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2378,22 +2372,22 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473072</v>
+        <v>472957</v>
       </c>
       <c r="R17" t="n">
-        <v>7023730</v>
+        <v>7023584</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,7 +2416,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2432,12 +2426,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,7 +2458,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883162</v>
+        <v>133880787</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2500,17 +2494,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472936</v>
+        <v>472964</v>
       </c>
       <c r="R18" t="n">
-        <v>7024244</v>
+        <v>7023790</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2539,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2549,7 +2543,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2581,7 +2575,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133882938</v>
+        <v>133880841</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2617,17 +2611,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472887</v>
+        <v>472964</v>
       </c>
       <c r="R19" t="n">
-        <v>7024233</v>
+        <v>7023791</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2656,7 +2650,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2660,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2698,7 +2692,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133882856</v>
+        <v>133880910</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2734,17 +2728,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472936</v>
+        <v>472977</v>
       </c>
       <c r="R20" t="n">
-        <v>7024232</v>
+        <v>7023797</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,12 +2777,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran, äldre och färska</t>
+          <t>Rikligt med ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,7 +2809,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133881340</v>
+        <v>133881025</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2846,7 +2840,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2855,13 +2849,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473047</v>
+        <v>472989</v>
       </c>
       <c r="R21" t="n">
-        <v>7023739</v>
+        <v>7023791</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,12 +2894,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med både färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883043</v>
+        <v>133881060</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2963,19 +2957,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Aspås, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472887</v>
+        <v>473002</v>
       </c>
       <c r="R22" t="n">
-        <v>7024224</v>
+        <v>7023782</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3011,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack och födosöksspår på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,7 +3043,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133880505</v>
+        <v>133881092</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -3085,17 +3079,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472957</v>
+        <v>473008</v>
       </c>
       <c r="R23" t="n">
-        <v>7023584</v>
+        <v>7023763</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3134,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3166,7 +3160,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133881577</v>
+        <v>133881273</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -3206,10 +3200,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473086</v>
+        <v>473036</v>
       </c>
       <c r="R24" t="n">
-        <v>7023722</v>
+        <v>7023744</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3241,7 +3235,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3251,7 +3245,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3400,7 +3394,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133881616</v>
+        <v>133881340</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3431,7 +3425,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3440,13 +3434,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473083</v>
+        <v>473047</v>
       </c>
       <c r="R26" t="n">
-        <v>7023715</v>
+        <v>7023739</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3475,7 +3469,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3485,12 +3479,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på bra</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,7 +3511,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133884248</v>
+        <v>133881460</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3548,7 +3542,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3557,13 +3551,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472989</v>
+        <v>473072</v>
       </c>
       <c r="R27" t="n">
-        <v>7024136</v>
+        <v>7023730</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3592,7 +3586,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3602,12 +3596,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,7 +3628,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133880910</v>
+        <v>133881577</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3674,13 +3668,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472977</v>
+        <v>473086</v>
       </c>
       <c r="R28" t="n">
-        <v>7023797</v>
+        <v>7023722</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3709,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,12 +3713,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3748,6 +3742,2106 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133881616</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473083</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7023715</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på bra</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133881690</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>473092</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7023702</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133881965</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>473101</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7023685</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133882634</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>472920</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7024099</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133882856</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>472936</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7024232</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre och färska</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133882938</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>472887</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7024233</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133883043</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>472887</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7024224</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack och födosöksspår på gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133883162</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>472936</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7024244</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133884248</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>472989</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7024136</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133884534</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>473064</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7023842</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133884656</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>473089</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7023872</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133884713</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>473086</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7023867</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133884805</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>473087</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7023868</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133884824</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>473089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7023870</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133884910</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>473087</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7023867</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133885500</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>473040</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7023508</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133881015</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hamptjärnen, Hamptjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>472989</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7023787</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133880251</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hamptjärnbäcken, Hamptjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>472980</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7023561</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
